--- a/basedatos_partidas/salida/descompuestos/CT-02-13-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-13-050.xlsx
@@ -591,10 +591,10 @@
         <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="15">
@@ -880,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>11.01</v>
+        <v>10.89</v>
       </c>
       <c r="H27" t="n">
         <v>0.11</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-02-13-050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-02-13-050.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 02 Demoliciones y desmontajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Techos y cubiertas</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
